--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_44_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_44_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2044</v>
+        <v>6.1715</v>
       </c>
       <c r="E2" t="n">
-        <v>8.252599999999999</v>
+        <v>8.4885</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0482</v>
+        <v>-2.317</v>
       </c>
       <c r="G2" t="n">
         <v>5.9949</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1942</v>
+        <v>0.1612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2513</v>
+        <v>-0.0154</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4455</v>
+        <v>0.1766</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3302</v>
+        <v>0.8433</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6783</v>
+        <v>0.7962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6519</v>
+        <v>0.047</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8757</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4286</v>
+        <v>0.9416</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1458</v>
+        <v>0.2638</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2828</v>
+        <v>0.6778</v>
       </c>
       <c r="V3" t="n">
         <v>1.0093</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9919</v>
+        <v>0.2688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2473</v>
+        <v>0.232</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7758</v>
+        <v>0.0368</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1104</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3346</v>
+        <v>0.0368</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4655</v>
+        <v>0.0368</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5391</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6897</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4287</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6258</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0682</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4424</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2688</v>
+        <v>-0.0196</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0368</v>
+        <v>-0.435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.232</v>
+        <v>0.4154</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0368</v>
+        <v>-0.7758</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1.1104</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0368</v>
+        <v>0.3346</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0368</v>
+        <v>-1.4655</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-1.5391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.6897</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.4287</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.8887</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.2743</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9678</v>
+        <v>-0.2437</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6853</v>
+        <v>-1.0955</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7175</v>
+        <v>0.8519</v>
       </c>
       <c r="G6" t="n">
         <v>0.0276</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2274</v>
+        <v>-0.5032</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4059</v>
+        <v>-0.2715</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1174</v>
+        <v>-0.7471</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7776</v>
+        <v>4.0135</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.895</v>
+        <v>-4.7605</v>
       </c>
       <c r="G7" t="n">
         <v>1.2958</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4358</v>
+        <v>0.8061</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5272</v>
+        <v>0.7631</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0914</v>
+        <v>0.0431</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9933</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3143</v>
+        <v>-1.769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.355</v>
+        <v>0.0011</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6693</v>
+        <v>-1.7701</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2471</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6286</v>
+        <v>0.174</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6018</v>
+        <v>0.248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0268</v>
+        <v>-0.074</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5561</v>
+        <v>-2.0142</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5594</v>
+        <v>-2.603</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9967</v>
+        <v>0.5888</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9193</v>
+        <v>-0.5114</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2065</v>
+        <v>0.4791</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7127</v>
+        <v>-0.9905</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.055</v>
+        <v>-1.4119</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3422</v>
+        <v>0.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>-1.4623</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1357</v>
+        <v>0.9005</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1357</v>
+        <v>0.4287</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1312</v>
+        <v>-0.575</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4233</v>
+        <v>-0.0314</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2921</v>
+        <v>-0.5436</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2183</v>
+        <v>-2.2302</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5905</v>
+        <v>-1.2671</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6277</v>
+        <v>-0.9631</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0122</v>
+        <v>-2.9193</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4731</v>
+        <v>-2.2065</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4852</v>
+        <v>-0.7127</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3981</v>
+        <v>-3.055</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0336</v>
+        <v>-2.3422</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4317</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>0.386</v>
+        <v>0.1357</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4395</v>
+        <v>0.1357</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0535</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7872</v>
+        <v>0.4571</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9673</v>
+        <v>0.7156</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1801</v>
+        <v>-0.2585</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0655</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0655</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.233</v>
+        <v>-2.2526</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.721</v>
+        <v>-0.8264</v>
       </c>
       <c r="F11" t="n">
-        <v>0.488</v>
+        <v>-1.4261</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5114</v>
+        <v>-0.0122</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4791</v>
+        <v>0.4731</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9905</v>
+        <v>-0.4852</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4119</v>
+        <v>-0.3981</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0504</v>
+        <v>0.0336</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4623</v>
+        <v>-0.4317</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9005</v>
+        <v>0.386</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4287</v>
+        <v>0.4395</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4718</v>
+        <v>-0.0535</v>
       </c>
       <c r="P11" t="n">
         <v>-0.9278</v>
@@ -1312,22 +1312,22 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7938</v>
+        <v>0.753</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6445</v>
+        <v>0.0215</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.0655</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.0655</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0655</v>
+        <v>-2.3749</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.327</v>
+        <v>-2.7372</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2615</v>
+        <v>0.3623</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5627</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7947</v>
+        <v>1.4853</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3031</v>
+        <v>0.8929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4916</v>
+        <v>0.5924</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4572</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3764</v>
+        <v>-5.6859</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0616</v>
+        <v>-4.4718</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3149</v>
+        <v>-1.2141</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2086</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1656</v>
+        <v>0.8562</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4086</v>
+        <v>0.1812</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5742</v>
+        <v>0.675</v>
       </c>
       <c r="V13" t="n">
         <v>0.3624</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.0535</v>
+        <v>-10.0536</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1000000000000014</v>
+        <v>-0.09989999999999988</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.953599999999998</v>
+        <v>-9.953500000000002</v>
       </c>
       <c r="G14" t="n">
         <v>-8.7577</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1077000000000002</v>
+        <v>-0.1076999999999994</v>
       </c>
       <c r="I14" t="n">
         <v>-8.649799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>4.073</v>
+        <v>4.072999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.282799999999999</v>
+        <v>-2.2828</v>
       </c>
       <c r="L14" t="n">
-        <v>6.356</v>
+        <v>6.356000000000002</v>
       </c>
       <c r="M14" t="n">
         <v>-12.8308</v>
@@ -1546,13 +1546,13 @@
         <v>10.4382</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1705</v>
+        <v>5.170700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4059</v>
+        <v>4.406199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7645</v>
+        <v>0.7645000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1469</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4198</v>
+        <v>5.2251</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8256</v>
+        <v>4.0921</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5943</v>
+        <v>1.133</v>
       </c>
       <c r="G15" t="n">
-        <v>0.994</v>
+        <v>5.3683</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8368</v>
+        <v>-0.3935</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1573</v>
+        <v>5.7618</v>
       </c>
       <c r="J15" t="n">
-        <v>1.476</v>
+        <v>5.3577</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1043</v>
+        <v>-0.5679</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3717</v>
+        <v>5.9256</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.482</v>
+        <v>0.0106</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.1744</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2144</v>
+        <v>-0.1638</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8149</v>
+        <v>0.3027</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4525</v>
+        <v>-0.1059</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3624</v>
+        <v>0.4086</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0748</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4621</v>
+        <v>4.1395</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3844</v>
+        <v>3.4863</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.6532</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3683</v>
+        <v>3.7418</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3935</v>
+        <v>2.8619</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7618</v>
+        <v>0.8799</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3577</v>
+        <v>3.281</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5679</v>
+        <v>2.7091</v>
       </c>
       <c r="L16" t="n">
-        <v>5.9256</v>
+        <v>0.5719</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0106</v>
+        <v>0.4608</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1744</v>
+        <v>0.1528</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1638</v>
+        <v>0.308</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4602</v>
+        <v>-0.9761</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>-0.3851</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6466</v>
+        <v>-0.5911</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2912</v>
+        <v>3.7356</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4136</v>
+        <v>2.3538</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1224</v>
+        <v>1.3819</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2618</v>
+        <v>0.994</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2448</v>
+        <v>0.8368</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5066</v>
+        <v>0.1573</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0803</v>
+        <v>1.476</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1155</v>
+        <v>0.1043</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1958</v>
+        <v>1.3717</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8185</v>
+        <v>-0.482</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1294</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6891</v>
+        <v>-1.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0114</v>
+        <v>0.1307</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7389</v>
+        <v>-0.0193</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7503</v>
+        <v>0.15</v>
       </c>
       <c r="V17" t="n">
+        <v>3.0748</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.2166</v>
+      </c>
+      <c r="X17" t="n">
         <v>-0.1418</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.789</v>
+        <v>3.72</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0346</v>
+        <v>3.8854</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2456</v>
+        <v>-0.1654</v>
       </c>
       <c r="G18" t="n">
-        <v>3.8807</v>
+        <v>2.2618</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2649</v>
+        <v>-1.2448</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6158</v>
+        <v>3.5066</v>
       </c>
       <c r="J18" t="n">
-        <v>5.5386</v>
+        <v>3.0803</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1831</v>
+        <v>-1.1155</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3555</v>
+        <v>4.1958</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.658</v>
+        <v>-0.8185</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0818</v>
+        <v>-0.1294</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7398</v>
+        <v>-0.6891</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3958</v>
+        <v>0.4402</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1845</v>
+        <v>-0.2671</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2113</v>
+        <v>0.7073</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.764</v>
+        <v>3.3274</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1324</v>
+        <v>3.2705</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3684</v>
+        <v>0.0569</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7418</v>
+        <v>3.8807</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8619</v>
+        <v>3.2649</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8799</v>
+        <v>0.6158</v>
       </c>
       <c r="J19" t="n">
-        <v>3.281</v>
+        <v>5.5386</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7091</v>
+        <v>3.1831</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5719</v>
+        <v>2.3555</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4608</v>
+        <v>-1.658</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1528</v>
+        <v>0.0818</v>
       </c>
       <c r="O19" t="n">
-        <v>0.308</v>
+        <v>-1.7398</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3516</v>
+        <v>0.1426</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>0.0514</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6127</v>
+        <v>0.0912</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2529</v>
+        <v>-0.1013</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1865</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0664</v>
+        <v>-0.0328</v>
       </c>
       <c r="G20" t="n">
         <v>-1.025</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2278</v>
+        <v>-1.0763</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7050999999999999</v>
+        <v>-0.6715</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3214</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5587</v>
+        <v>-1.9099</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2374</v>
+        <v>1.3237</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4595</v>
+        <v>1.5752</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.723</v>
+        <v>-1.3961</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7365</v>
+        <v>2.9713</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9447</v>
+        <v>0.7319</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7401</v>
+        <v>-1.7709</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2046</v>
+        <v>2.5027</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5147</v>
+        <v>0.8433</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0171</v>
+        <v>0.3748</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5319</v>
+        <v>0.4685</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9241</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3318</v>
+        <v>-0.3222</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4077</v>
+        <v>-0.4474</v>
       </c>
       <c r="V21" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1197</v>
+        <v>-1.1191</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4566</v>
+        <v>-2.21</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6631</v>
+        <v>1.0909</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9454</v>
+        <v>-3.4595</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2797</v>
+        <v>-1.723</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-1.7365</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6455</v>
+        <v>-2.9447</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7191</v>
+        <v>-1.7401</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>-1.2046</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2999</v>
+        <v>-0.5147</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4395</v>
+        <v>0.0171</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.5319</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4938</v>
+        <v>1.1264</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1889</v>
+        <v>0.6805</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6827</v>
+        <v>0.4459</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6585</v>
+        <v>-1.4063</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0278</v>
+        <v>-0.8105</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3693</v>
+        <v>-0.5959</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5752</v>
+        <v>-0.9454</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3961</v>
+        <v>-0.2797</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9713</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7319</v>
+        <v>-0.6455</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7709</v>
+        <v>-0.7191</v>
       </c>
       <c r="L23" t="n">
-        <v>2.5027</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8433</v>
+        <v>-0.2999</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3748</v>
+        <v>0.4395</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4685</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3917</v>
+        <v>1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.842</v>
+        <v>-0.7804</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>-0.165</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4018</v>
+        <v>-0.6155</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3202</v>
+        <v>-2.9492</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6073</v>
+        <v>-2.1355</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7129</v>
+        <v>-0.8137</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6343</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1498</v>
+        <v>0.2212</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>0.1731</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.0534</v>
+        <v>13.9855</v>
       </c>
       <c r="E25" t="n">
-        <v>9.9537</v>
+        <v>9.953700000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09999999999999998</v>
+        <v>4.0318</v>
       </c>
       <c r="G25" t="n">
         <v>8.757600000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1077000000000004</v>
+        <v>0.1077000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>8.649699999999999</v>
+        <v>8.649700000000001</v>
       </c>
       <c r="J25" t="n">
         <v>12.8308</v>
@@ -2392,7 +2392,7 @@
         <v>2.2828</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.3562</v>
+        <v>-6.356199999999999</v>
       </c>
       <c r="P25" t="n">
         <v>2.3196</v>
@@ -2404,19 +2404,19 @@
         <v>12.7574</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.170599999999999</v>
+        <v>-1.2387</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7644000000000003</v>
+        <v>-0.7644</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.4063</v>
+        <v>-0.4744000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>4.147</v>
       </c>
       <c r="W25" t="n">
-        <v>8.325100000000001</v>
+        <v>8.325099999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-4.178100000000001</v>
